--- a/TC_Compound_Data.xlsx
+++ b/TC_Compound_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jacobcn2\Documents\Thermal Conductivity Model\Code\TC_Comparison_Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveutk-my.sharepoint.com/personal/jnumbers_vols_utk_edu/Documents/Documents/2026-Structural-Coherence-Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A296B76C-EC5B-4344-9591-344623A2D40F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{A296B76C-EC5B-4344-9591-344623A2D40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51C95423-5C08-4E63-A31D-E822FF9E101F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,19 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -29,19 +42,10 @@
   <commentList>
     <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{0F2A2AAB-6BDF-4416-8CAD-D9A0BFB1B917}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Source: Ionic radius data from R. D. Shannon, “Revised effective ionic radii and systematic studies of interatomic distances in halides and chalcogenides,” Acta Crystallographica 32, no. 5 (1976): 751–767.</t>
-        </r>
       </text>
     </comment>
     <comment ref="AQ6" authorId="1" shapeId="0" xr:uid="{8534754D-6E22-406C-8C2D-6B066F351040}">
@@ -1378,7 +1382,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="V1" dT="2025-10-09T09:58:25.59" personId="{D840FA81-CD01-4E89-B2EB-0BCA2B05220B}" id="{0F2A2AAB-6BDF-4416-8CAD-D9A0BFB1B917}">
+  <threadedComment ref="Z1" dT="2025-10-09T09:58:25.59" personId="{D840FA81-CD01-4E89-B2EB-0BCA2B05220B}" id="{0F2A2AAB-6BDF-4416-8CAD-D9A0BFB1B917}">
     <text>Source: Ionic radius data from R. D. Shannon, “Revised effective ionic radii and systematic studies of interatomic distances in halides and chalcogenides,” Acta Crystallographica 32, no. 5 (1976): 751–767.</text>
   </threadedComment>
 </ThreadedComments>
@@ -1435,6 +1439,7 @@
     <col min="41" max="41" width="2.7109375" style="28" customWidth="1"/>
     <col min="42" max="42" width="11.5703125" style="16" customWidth="1"/>
     <col min="45" max="45" width="2.7109375" style="22" customWidth="1"/>
+    <col min="46" max="46" width="13.28515625" customWidth="1"/>
     <col min="47" max="47" width="9.7109375" customWidth="1"/>
     <col min="48" max="48" width="2.7109375" style="22" customWidth="1"/>
   </cols>
@@ -2090,7 +2095,13 @@
       <c r="AR5" s="47">
         <v>0</v>
       </c>
-      <c r="AT5" s="21"/>
+      <c r="AT5" s="21">
+        <f>AN5/1000000</f>
+        <v>2.9262240896358542</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
       <c r="AW5" s="20">
         <v>5.36</v>
       </c>
@@ -4205,6 +4216,10 @@
       <c r="AA25" s="35"/>
       <c r="AD25" s="19"/>
       <c r="AE25" s="35"/>
+      <c r="AN25" s="16">
+        <f>AVERAGE(AN2:AN23)</f>
+        <v>2680541.4756652657</v>
+      </c>
       <c r="AT25" s="2"/>
       <c r="AU25" s="8"/>
     </row>
